--- a/output/pdf_financials_xlsx/POWR.xlsx
+++ b/output/pdf_financials_xlsx/POWR.xlsx
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.539139</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.263427</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.404371</v>
       </c>
     </row>
     <row r="93">
@@ -3063,7 +3063,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3375,7 +3379,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.539139</v>
       </c>

--- a/output/pdf_financials_xlsx/POWR.xlsx
+++ b/output/pdf_financials_xlsx/POWR.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001465</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
     </row>
     <row r="13">
@@ -866,10 +866,10 @@
         <v>-1.948356</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.37769</v>
+        <v>-5.379155</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.335691</v>
+        <v>-0.335696</v>
       </c>
     </row>
     <row r="28">
@@ -898,10 +898,10 @@
         <v>-1.948356</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.37769</v>
+        <v>-5.379155</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.335691</v>
+        <v>-0.335696</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.075124</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004298</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.01584</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.075124</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.004298</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.01584</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.089059</v>
+        <v>0.013935</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011443</v>
+        <v>0.007145</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.024303</v>
+        <v>0.008463</v>
       </c>
     </row>
     <row r="49">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">

--- a/output/pdf_financials_xlsx/POWR.xlsx
+++ b/output/pdf_financials_xlsx/POWR.xlsx
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.638145</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.314273</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.456979</v>
       </c>
     </row>
     <row r="65">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.052816</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.068041</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008643</v>
       </c>
     </row>
     <row r="102">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.638099</v>
+        <v>0.585283</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.026782</v>
+        <v>0.041259</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.132388</v>
+        <v>0.141031</v>
       </c>
     </row>
     <row r="107">
@@ -3732,7 +3732,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.052816</v>
       </c>
